--- a/survey_templates/049_home_security_survey--survey_templates.xlsx
+++ b/survey_templates/049_home_security_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Home Security Survey</t>
+          <t>What are you trying to accomplish with this survey?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>goals</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What are you trying to accomplish with this survey?</t>
+          <t>Contact Information</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>security_features</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Contact Information</t>
+          <t>Security Features</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>security_features</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Security Features</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>additional_comments</t>
+          <t>contact_number</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>Contact Number</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>security_survey_rating</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Contact Number</t>
+          <t>Security Survey Rating</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>security_features_1</t>
+          <t>client_signature</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Security Features</t>
+          <t>Client Signature</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>security_features_2</t>
+          <t>security_features_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Security Features</t>
+          <t>Security Features 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>security_features_3</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Security Features</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>security_survey_rating_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Security Survey Rating 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,182 +837,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>security_survey_rating</t>
+          <t>additional_notes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Security Survey Rating</t>
+          <t>Additional Notes</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>additional_notes</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Additional Notes</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>security_survey_rating_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Security Survey Rating</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>client_signature</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Client Signature</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>security_features_4</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Security Features</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>security_features_5</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Security Features</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>security_features_6</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Security Features</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1029,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1057,527 +896,221 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>home_security_survey_2_choices</t>
+          <t>security_features_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>home_security_survey_2_choices</t>
+          <t>security_features_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>home_security_survey_2_choices</t>
+          <t>security_survey_rating_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>contact_info_choices</t>
+          <t>security_survey_rating_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>contact_info_choices</t>
+          <t>security_survey_rating_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>contact_info_choices</t>
+          <t>security_survey_rating_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>security_features_choices</t>
+          <t>security_features_1_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>motion-sensitive_lighting</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Motion-sensitive lighting</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>security_features_choices</t>
+          <t>security_features_1_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>security_cameras</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>Security cameras</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>security_features_choices</t>
+          <t>security_features_1_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>alarm_system</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>Alarm system</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>security_features_1_choices</t>
+          <t>security_survey_rating_1_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>security_features_1_choices</t>
+          <t>security_survey_rating_1_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option11</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option11</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>security_features_1_choices</t>
+          <t>security_survey_rating_1_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option12</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option12</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>security_features_2_choices</t>
+          <t>security_survey_rating_1_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option13</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option13</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>security_features_2_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>option14</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>option14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>security_features_2_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>option15</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>option15</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>security_features_3_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>option16</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>option16</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>security_features_3_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>option17</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>option17</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>security_features_3_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>option18</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>option18</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>security_survey_rating_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>option19</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>option19</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>security_survey_rating_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>option20</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>option20</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>security_survey_rating_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>option21</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>option21</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>security_survey_rating_2_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>option22</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>option22</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>security_survey_rating_2_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>option23</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>option23</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>security_survey_rating_2_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>option24</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>option24</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>security_features_4_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>option25</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>option25</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>security_features_4_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>option26</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>option26</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>security_features_4_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>option27</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>option27</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>security_features_5_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>security_features_5_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>security_features_6_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>security_features_6_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
